--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_201_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_201_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9047</v>
+        <v>8.0585</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8315</v>
+        <v>6.3295</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0732</v>
+        <v>1.729</v>
       </c>
       <c r="G2" t="n">
         <v>0.3928</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5273</v>
+        <v>2.6811</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5637</v>
+        <v>1.0618</v>
       </c>
       <c r="U2" t="n">
-        <v>2.9635</v>
+        <v>1.6193</v>
       </c>
       <c r="V2" t="n">
         <v>4.2888</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9216</v>
+        <v>7.7814</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2621</v>
+        <v>6.7522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6595</v>
+        <v>1.0292</v>
       </c>
       <c r="G3" t="n">
         <v>4.1365</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0145</v>
+        <v>1.8743</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6563</v>
+        <v>0.8338</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6708</v>
+        <v>1.0405</v>
       </c>
       <c r="V3" t="n">
         <v>2.0026</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5892</v>
+        <v>3.3761</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3382</v>
+        <v>4.1587</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.749</v>
+        <v>-0.7826</v>
       </c>
       <c r="G4" t="n">
         <v>1.4591</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7021</v>
+        <v>1.489</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0603</v>
+        <v>0.8808</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6418</v>
+        <v>0.6082</v>
       </c>
       <c r="V4" t="n">
         <v>1.3558</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SANLI</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6932</v>
+        <v>2.3001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5015</v>
+        <v>0.4038</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8083</v>
+        <v>1.8963</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2857</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2857</v>
+        <v>-1.0242</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.5659</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.8457</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7897999999999999</v>
+        <v>-1.0413</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.887</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5041</v>
+        <v>-0.3039</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5041</v>
+        <v>0.0171</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.3211</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7117</v>
+        <v>1.7917</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7117</v>
+        <v>0.7512</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.0405</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>2.2862</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6326000000000001</v>
+        <v>1.0605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4508</v>
+        <v>0.6435</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1818</v>
+        <v>0.417</v>
       </c>
       <c r="G6" t="n">
         <v>-0.08110000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.554</v>
+        <v>0.9818</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1889</v>
+        <v>0.3815</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3651</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4403</v>
+        <v>0.3558</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0863</v>
+        <v>2.6254</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5266</v>
+        <v>-2.2696</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5417999999999999</v>
+        <v>-0.9958</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0058</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5659</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8457</v>
+        <v>0.2306</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0413</v>
+        <v>-0.0469</v>
       </c>
       <c r="L7" t="n">
-        <v>1.887</v>
+        <v>0.2775</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3039</v>
+        <v>-1.2264</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0171</v>
+        <v>-0.9588</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3211</v>
+        <v>-0.2676</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06809999999999999</v>
+        <v>1.5657</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7389</v>
+        <v>0.7866</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6708</v>
+        <v>0.7791</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2862</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2862</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>S. SANLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3923</v>
+        <v>0.2214</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8299</v>
+        <v>1.0297</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4376</v>
+        <v>-0.8083</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9958</v>
+        <v>0.2857</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0058</v>
+        <v>0.2857</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009900000000000001</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2306</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0469</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2775</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2264</v>
+        <v>-0.5041</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9588</v>
+        <v>-0.5041</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2676</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6021</v>
+        <v>0.2399</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9911</v>
+        <v>0.2399</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6111</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2862</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.007</v>
+        <v>-0.2966</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5107</v>
+        <v>0.3563</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5037</v>
+        <v>-0.6529</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8294</v>
+        <v>-0.7546</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2004</v>
+        <v>-0.1991</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.629</v>
+        <v>-0.5555</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6892</v>
+        <v>-0.0252</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7997</v>
+        <v>0.3697</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1104</v>
+        <v>-0.3949</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1401</v>
+        <v>-0.7294</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4008</v>
+        <v>-0.5688</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.1605</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2863</v>
+        <v>0.8138</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3383</v>
+        <v>0.3815</v>
       </c>
       <c r="U9" t="n">
-        <v>0.948</v>
+        <v>0.4323</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0954</v>
+        <v>-1.0235</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3081</v>
+        <v>-1.3928</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7873</v>
+        <v>0.3693</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7546</v>
+        <v>-1.8294</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1991</v>
+        <v>-1.2004</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5555</v>
+        <v>-0.629</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0252</v>
+        <v>-0.6892</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3697</v>
+        <v>-0.7997</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3949</v>
+        <v>0.1104</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7294</v>
+        <v>-1.1401</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5688</v>
+        <v>-0.4008</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1605</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0149</v>
+        <v>1.2698</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2829</v>
+        <v>0.4562</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2978</v>
+        <v>0.8136</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7928</v>
+        <v>-1.6173</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8406</v>
+        <v>-0.7659</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9523</v>
+        <v>-0.8514</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7107</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0934</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1415</v>
+        <v>-0.0668</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0593</v>
+        <v>0.1601</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4824</v>
+        <v>-4.2733</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7845</v>
+        <v>-3.7098</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6979</v>
+        <v>-0.5635</v>
       </c>
       <c r="G12" t="n">
         <v>-2.245</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2917</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3734</v>
+        <v>-0.2987</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2161</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.1963</v>
+        <v>15.9431</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6838</v>
+        <v>16.4306</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4876000000000006</v>
+        <v>-0.4875</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8006999999999991</v>
@@ -1441,7 +1441,7 @@
         <v>-5.001899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>7.403600000000001</v>
+        <v>7.403600000000003</v>
       </c>
       <c r="K13" t="n">
         <v>8.4246</v>
@@ -1465,16 +1465,16 @@
         <v>-9.2782</v>
       </c>
       <c r="R13" t="n">
-        <v>5.799099999999999</v>
+        <v>5.7991</v>
       </c>
       <c r="S13" t="n">
-        <v>11.971</v>
+        <v>12.7179</v>
       </c>
       <c r="T13" t="n">
-        <v>4.661</v>
+        <v>5.4078</v>
       </c>
       <c r="U13" t="n">
-        <v>7.309899999999999</v>
+        <v>7.31</v>
       </c>
       <c r="V13" t="n">
         <v>7.505400000000001</v>
@@ -1483,7 +1483,7 @@
         <v>12.8975</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.3921</v>
+        <v>-5.392100000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4888</v>
+        <v>2.9213</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3681</v>
+        <v>4.486</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8793</v>
+        <v>-1.5647</v>
       </c>
       <c r="G14" t="n">
         <v>3.682</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0129</v>
+        <v>-1.5804</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2617</v>
+        <v>-1.1437</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7512</v>
+        <v>-0.4367</v>
       </c>
       <c r="V14" t="n">
         <v>0.8197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6589</v>
+        <v>1.1922</v>
       </c>
       <c r="E15" t="n">
-        <v>4.178</v>
+        <v>4.2959</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5191</v>
+        <v>-3.1037</v>
       </c>
       <c r="G15" t="n">
         <v>4.5684</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3166</v>
+        <v>-0.7833</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.845</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3536</v>
+        <v>0.0617</v>
       </c>
       <c r="V15" t="n">
         <v>-3.7527</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4912</v>
+        <v>0.5584</v>
       </c>
       <c r="E16" t="n">
         <v>0.9082</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.417</v>
+        <v>-0.3498</v>
       </c>
       <c r="G16" t="n">
         <v>0.1318</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1274</v>
+        <v>0.1946</v>
       </c>
       <c r="T16" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MAHMUTOGLU</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6249</v>
+        <v>-0.1936</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4855</v>
+        <v>-0.0127</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1104</v>
+        <v>-0.1809</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7498</v>
+        <v>-0.9179</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2473</v>
+        <v>-0.9915</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9971</v>
+        <v>0.0736</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3228</v>
+        <v>0.0155</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1091</v>
+        <v>-0.3256</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7863</v>
+        <v>0.3412</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0726</v>
+        <v>-0.9334</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8618</v>
+        <v>-0.6659</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2108</v>
+        <v>-0.2676</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6431</v>
+        <v>-1.9716</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3734</v>
+        <v>-1.1005</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2697</v>
+        <v>-0.8711</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>M. MAHMUTOGLU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9457</v>
+        <v>-0.4397</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2486</v>
+        <v>0.6034</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-1.0432</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9179</v>
+        <v>-0.7498</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9915</v>
+        <v>0.2473</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0736</v>
+        <v>-0.9971</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0155</v>
+        <v>0.3228</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3256</v>
+        <v>1.1091</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3412</v>
+        <v>-0.7863</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9334</v>
+        <v>-1.0726</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6659</v>
+        <v>-0.8618</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2676</v>
+        <v>-0.2108</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7237</v>
+        <v>-0.458</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3364</v>
+        <v>-0.2555</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3873</v>
+        <v>-0.2025</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3124</v>
+        <v>-2.2661</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.91</v>
+        <v>-0.6741</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4025</v>
+        <v>-1.592</v>
       </c>
       <c r="G19" t="n">
         <v>0.3701</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7005</v>
+        <v>-1.6542</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4936</v>
+        <v>-1.2577</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2069</v>
+        <v>-0.3965</v>
       </c>
       <c r="V19" t="n">
         <v>-1.214</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4123</v>
+        <v>-2.3786</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6156</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7967</v>
+        <v>-0.7631</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6565</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0303</v>
+        <v>0.0639</v>
       </c>
       <c r="T20" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V20" t="n">
         <v>0.1418</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7917</v>
+        <v>-2.9928</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7353</v>
+        <v>-0.138</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0563</v>
+        <v>-2.8548</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1097</v>
+        <v>0.5636</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0923</v>
+        <v>0.6338</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0173</v>
+        <v>-0.0702</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4015</v>
+        <v>1.4183</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1379</v>
+        <v>1.3815</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5394</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.8547</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2303</v>
+        <v>-0.7477</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5221</v>
+        <v>-0.107</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3958</v>
+        <v>-1.0899</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3339</v>
+        <v>-0.5384</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0619</v>
+        <v>-0.5515</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.214</v>
+        <v>-2.0026</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8742</v>
+        <v>-3.008</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2158</v>
+        <v>-2.9977</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.09</v>
+        <v>-0.0102</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5636</v>
+        <v>-1.2095</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6338</v>
+        <v>-1.0657</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0702</v>
+        <v>-0.1438</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4183</v>
+        <v>-0.6549</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3815</v>
+        <v>-0.5679</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0368</v>
+        <v>-0.0871</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8547</v>
+        <v>-0.5546</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7477</v>
+        <v>-0.4978</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.107</v>
+        <v>-0.0568</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-2.1928</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1845</v>
+        <v>-1.183</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-1.0097</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0026</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2821</v>
+        <v>-3.1791</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3888</v>
+        <v>-2.0892</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8933</v>
+        <v>-1.0899</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8719</v>
+        <v>-2.1097</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3638</v>
+        <v>-1.0923</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4919</v>
+        <v>-1.0173</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4284</v>
+        <v>-1.4015</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.502</v>
+        <v>0.1379</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0736</v>
+        <v>-1.5394</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4435</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8618</v>
+        <v>-1.2303</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4183</v>
+        <v>0.5221</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4121</v>
+        <v>-0.7833</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0395</v>
+        <v>-0.6877</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3725</v>
+        <v>-0.0955</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2862</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2862</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.592</v>
+        <v>-3.8376</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2336</v>
+        <v>-1.7427</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3584</v>
+        <v>-2.0949</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2095</v>
+        <v>-1.8719</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0657</v>
+        <v>-2.3638</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1438</v>
+        <v>0.4919</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6549</v>
+        <v>-1.4284</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5679</v>
+        <v>-1.502</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0871</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5546</v>
+        <v>-0.4435</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4978</v>
+        <v>-0.8618</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0568</v>
+        <v>0.4183</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7768</v>
+        <v>-0.1434</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4189</v>
+        <v>-0.3143</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3579</v>
+        <v>0.1709</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3943</v>
+        <v>-2.2862</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3943</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="25">
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.1964</v>
+        <v>-13.6236</v>
       </c>
       <c r="E25" t="n">
-        <v>1.023699999999998</v>
+        <v>1.023500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.2201</v>
+        <v>-14.6472</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8005999999999986</v>
+        <v>0.8005999999999978</v>
       </c>
       <c r="H25" t="n">
         <v>-4.2013</v>
       </c>
       <c r="I25" t="n">
-        <v>5.0021</v>
+        <v>5.002100000000001</v>
       </c>
       <c r="J25" t="n">
         <v>8.2041</v>
@@ -2383,13 +2383,13 @@
         <v>4.2235</v>
       </c>
       <c r="L25" t="n">
-        <v>3.980800000000001</v>
+        <v>3.980799999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-7.4034</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.424800000000001</v>
+        <v>-8.424799999999999</v>
       </c>
       <c r="O25" t="n">
         <v>1.0213</v>
@@ -2404,16 +2404,16 @@
         <v>9.2784</v>
       </c>
       <c r="S25" t="n">
-        <v>-11.9709</v>
+        <v>-10.3984</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.310099999999999</v>
+        <v>-7.31</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.6609</v>
+        <v>-3.0882</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.5054</v>
+        <v>-7.505399999999999</v>
       </c>
       <c r="W25" t="n">
         <v>5.9282</v>
